--- a/Data/National Accounts/PSA-21OS_2018PSNA_Ann.xlsx
+++ b/Data/National Accounts/PSA-21OS_2018PSNA_Ann.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\Shared drives\QNAP\NAP Dissemination\As of January 2026\Tables\Prelim Q4 2025\NAP Q1 2000 to Q4 2025\Annl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\Shared drives\QNAP\NAP Dissemination\As of April 2026\Tables\NAP Q1 2000 to Q4 2025\Annl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC33DB20-7B03-45FB-A774-BDB7099E2A91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4332028-CFDE-4CF3-BCE1-4BFCC0606F1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="OS" sheetId="2" r:id="rId1"/>
@@ -619,10 +619,10 @@
     <t>Annual 2001 to 2024</t>
   </si>
   <si>
-    <t>As of January 2026</t>
+    <t>2024 - 2025</t>
   </si>
   <si>
-    <t>2024 - 2025</t>
+    <t>As of April 2026</t>
   </si>
 </sst>
 </file>
@@ -23621,7 +23621,7 @@
     </row>
     <row r="3" spans="1:96" s="3" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A3" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:96" s="3" customFormat="1" ht="15" x14ac:dyDescent="0.2">
@@ -23891,10 +23891,10 @@
         <v>275153.91537396394</v>
       </c>
       <c r="Z12" s="16">
-        <v>309994.43566739064</v>
+        <v>309511.60873040895</v>
       </c>
       <c r="AA12" s="16">
-        <v>341428.31305611547</v>
+        <v>341301.7718816417</v>
       </c>
       <c r="AB12" s="4"/>
       <c r="AC12" s="4"/>
@@ -24043,10 +24043,10 @@
         <v>189348.14360676933</v>
       </c>
       <c r="Z13" s="16">
-        <v>217474.05199936754</v>
+        <v>217443.02951513859</v>
       </c>
       <c r="AA13" s="16">
-        <v>233916.45830123394</v>
+        <v>233090.58692887018</v>
       </c>
       <c r="AB13" s="4"/>
       <c r="AC13" s="4"/>
@@ -24293,10 +24293,10 @@
         <v>464502.05898073327</v>
       </c>
       <c r="Z15" s="17">
-        <v>527468.48766675824</v>
+        <v>526954.63824554754</v>
       </c>
       <c r="AA15" s="17">
-        <v>575344.77135734935</v>
+        <v>574392.35881051188</v>
       </c>
       <c r="AB15" s="4"/>
       <c r="AC15" s="4"/>
@@ -24688,7 +24688,7 @@
     </row>
     <row r="22" spans="1:96" s="3" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -25088,10 +25088,10 @@
         <v>249366.63727548483</v>
       </c>
       <c r="Z31" s="16">
-        <v>271329.21966959495</v>
+        <v>270911.99523307651</v>
       </c>
       <c r="AA31" s="16">
-        <v>292892.99966398528</v>
+        <v>292778.37382464402</v>
       </c>
       <c r="AB31" s="4"/>
       <c r="AC31" s="4"/>
@@ -25240,10 +25240,10 @@
         <v>159704.01135621703</v>
       </c>
       <c r="Z32" s="16">
-        <v>175847.14787084068</v>
+        <v>175831.54672887363</v>
       </c>
       <c r="AA32" s="16">
-        <v>184060.49284676419</v>
+        <v>183657.19200167042</v>
       </c>
       <c r="AB32" s="4"/>
       <c r="AC32" s="4"/>
@@ -25490,10 +25490,10 @@
         <v>409070.64863170183</v>
       </c>
       <c r="Z34" s="17">
-        <v>447176.36754043563</v>
+        <v>446743.54196195013</v>
       </c>
       <c r="AA34" s="17">
-        <v>476953.49251074949</v>
+        <v>476435.56582631444</v>
       </c>
       <c r="AB34" s="4"/>
       <c r="AC34" s="4"/>
@@ -25885,7 +25885,7 @@
     </row>
     <row r="41" spans="1:96" s="3" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
@@ -26173,7 +26173,7 @@
         <v>46</v>
       </c>
       <c r="Z48" s="21" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AA48" s="21"/>
     </row>
@@ -26280,10 +26280,10 @@
         <v>26.69850339981727</v>
       </c>
       <c r="Y50" s="22">
-        <v>12.662193175072446</v>
+        <v>12.486717955566505</v>
       </c>
       <c r="Z50" s="22">
-        <v>10.140142458057497</v>
+        <v>10.271072959632562</v>
       </c>
       <c r="AA50" s="22"/>
       <c r="AB50" s="4"/>
@@ -26425,10 +26425,10 @@
         <v>27.12530957795758</v>
       </c>
       <c r="Y51" s="22">
-        <v>14.854071371837136</v>
+        <v>14.837687538524591</v>
       </c>
       <c r="Z51" s="22">
-        <v>7.5606290270961836</v>
+        <v>7.1961641854526306</v>
       </c>
       <c r="AA51" s="22"/>
       <c r="AB51" s="4"/>
@@ -26663,10 +26663,10 @@
         <v>26.872138828382859</v>
       </c>
       <c r="Y53" s="22">
-        <v>13.555683439637178</v>
+        <v>13.445059727368118</v>
       </c>
       <c r="Z53" s="22">
-        <v>9.0766149656390667</v>
+        <v>9.0022398745562668</v>
       </c>
       <c r="AA53" s="22"/>
       <c r="AB53" s="4"/>
@@ -27044,7 +27044,7 @@
     </row>
     <row r="60" spans="1:91" s="3" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
@@ -27332,7 +27332,7 @@
         <v>46</v>
       </c>
       <c r="Z67" s="9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AA67" s="9"/>
     </row>
@@ -27439,10 +27439,10 @@
         <v>21.017765125670508</v>
       </c>
       <c r="Y69" s="22">
-        <v>8.8073459361154249</v>
+        <v>8.6400322805771737</v>
       </c>
       <c r="Z69" s="22">
-        <v>7.9474595550929337</v>
+        <v>8.0713954997655151</v>
       </c>
       <c r="AA69" s="22"/>
       <c r="AB69" s="4"/>
@@ -27584,10 +27584,10 @@
         <v>19.707589916165375</v>
       </c>
       <c r="Y70" s="22">
-        <v>10.108159699643778</v>
+        <v>10.098390914354937</v>
       </c>
       <c r="Z70" s="22">
-        <v>4.6707297078006462</v>
+        <v>4.4506491686976375</v>
       </c>
       <c r="AA70" s="22"/>
       <c r="AB70" s="4"/>
@@ -27822,10 +27822,10 @@
         <v>20.50286550713885</v>
       </c>
       <c r="Y72" s="22">
-        <v>9.3151926289978064</v>
+        <v>9.2093855807695206</v>
       </c>
       <c r="Z72" s="22">
-        <v>6.658921877758047</v>
+        <v>6.6463241379979934</v>
       </c>
       <c r="AA72" s="22"/>
       <c r="AB72" s="4"/>
@@ -28178,7 +28178,7 @@
     </row>
     <row r="78" spans="1:96" s="3" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A78" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
@@ -28578,10 +28578,10 @@
         <v>110.34110993363997</v>
       </c>
       <c r="Z87" s="22">
-        <v>114.25029565370046</v>
+        <v>114.24802673064501</v>
       </c>
       <c r="AA87" s="22">
-        <v>116.57100492255232</v>
+        <v>116.57342290112595</v>
       </c>
       <c r="AB87" s="4"/>
       <c r="AC87" s="4"/>
@@ -28730,10 +28730,10 @@
         <v>118.56192089278935</v>
       </c>
       <c r="Z88" s="22">
-        <v>123.67220886579391</v>
+        <v>123.66553872748926</v>
       </c>
       <c r="AA88" s="22">
-        <v>127.08672821819309</v>
+        <v>126.91612258056854</v>
       </c>
       <c r="AB88" s="4"/>
       <c r="AC88" s="4"/>
@@ -28980,10 +28980,10 @@
         <v>113.55057140727247</v>
       </c>
       <c r="Z90" s="22">
-        <v>117.9553585463262</v>
+        <v>117.95461797418196</v>
       </c>
       <c r="AA90" s="22">
-        <v>120.62911382169663</v>
+        <v>120.56034435932681</v>
       </c>
       <c r="AB90" s="4"/>
       <c r="AC90" s="4"/>
@@ -29237,7 +29237,7 @@
     </row>
     <row r="97" spans="1:96" s="3" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A97" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B97" s="2"/>
       <c r="C97" s="2"/>
@@ -29637,10 +29637,10 @@
         <v>59.236317698513552</v>
       </c>
       <c r="Z106" s="22">
-        <v>58.770228537943972</v>
+        <v>58.735911265702597</v>
       </c>
       <c r="AA106" s="22">
-        <v>59.343254697634642</v>
+        <v>59.419622605779622</v>
       </c>
       <c r="AB106" s="4"/>
       <c r="AC106" s="4"/>
@@ -29789,10 +29789,10 @@
         <v>40.763682301486455</v>
       </c>
       <c r="Z107" s="22">
-        <v>41.229771462056014</v>
+        <v>41.264088734297403</v>
       </c>
       <c r="AA107" s="22">
-        <v>40.65674530236538</v>
+        <v>40.580377394220378</v>
       </c>
       <c r="AB107" s="4"/>
       <c r="AC107" s="4"/>
@@ -30434,7 +30434,7 @@
     </row>
     <row r="116" spans="1:96" s="3" customFormat="1" ht="15" x14ac:dyDescent="0.2">
       <c r="A116" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B116" s="2"/>
       <c r="C116" s="2"/>
@@ -30834,10 +30834,10 @@
         <v>60.959308156082557</v>
       </c>
       <c r="Z125" s="22">
-        <v>60.676108883383726</v>
+        <v>60.641502290849125</v>
       </c>
       <c r="AA125" s="22">
-        <v>61.409131972628153</v>
+        <v>61.451829969254845</v>
       </c>
       <c r="AB125" s="4"/>
       <c r="AC125" s="4"/>
@@ -30986,10 +30986,10 @@
         <v>39.04069184391745</v>
       </c>
       <c r="Z126" s="22">
-        <v>39.323891116616267</v>
+        <v>39.358497709150875</v>
       </c>
       <c r="AA126" s="22">
-        <v>38.590868027371847</v>
+        <v>38.548170030745148</v>
       </c>
       <c r="AB126" s="4"/>
       <c r="AC126" s="4"/>
